--- a/upload_data/회원-2026-09-20.xlsx
+++ b/upload_data/회원-2026-09-20.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21624" windowHeight="11916"/>
+    <workbookView windowWidth="21432" windowHeight="10176"/>
   </bookViews>
   <sheets>
-    <sheet name="회원-2026-09-20" sheetId="1" r:id="rId1"/>
+    <sheet name="member_template" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,129 +27,50 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t>회원명</t>
+    <t>이름</t>
+  </si>
+  <si>
+    <t>전화번호</t>
   </si>
   <si>
     <t>생년월일</t>
   </si>
   <si>
-    <t>전화번호</t>
-  </si>
-  <si>
     <t>성별</t>
   </si>
   <si>
-    <t>레벨</t>
+    <t>실력등급</t>
   </si>
   <si>
-    <t>요일1</t>
+    <t>레슨형태(개인,단체)</t>
   </si>
   <si>
-    <t>시간1</t>
+    <t>홍길동</t>
   </si>
   <si>
-    <t>요일2</t>
+    <t>010-1234-5678</t>
   </si>
   <si>
-    <t>시간2</t>
-  </si>
-  <si>
-    <t>요일3</t>
-  </si>
-  <si>
-    <t>시간3</t>
-  </si>
-  <si>
-    <t>요일4</t>
-  </si>
-  <si>
-    <t>시간4</t>
-  </si>
-  <si>
-    <t>구분</t>
-  </si>
-  <si>
-    <t>상태</t>
-  </si>
-  <si>
-    <t>가철수</t>
-  </si>
-  <si>
-    <t>010-1111-2222</t>
-  </si>
-  <si>
-    <t>남</t>
-  </si>
-  <si>
-    <t>중</t>
-  </si>
-  <si>
-    <t>월</t>
-  </si>
-  <si>
-    <t>화</t>
-  </si>
-  <si>
-    <t>목</t>
-  </si>
-  <si>
-    <t>금</t>
-  </si>
-  <si>
-    <t>사용자</t>
-  </si>
-  <si>
-    <t>이용중</t>
-  </si>
-  <si>
-    <t>나철수</t>
-  </si>
-  <si>
-    <t>010-1111-3333</t>
+    <t>여</t>
   </si>
   <si>
     <t>상</t>
   </si>
   <si>
-    <t>다철수</t>
-  </si>
-  <si>
-    <t>010-1111-4444</t>
-  </si>
-  <si>
-    <t>여</t>
-  </si>
-  <si>
-    <t>수</t>
-  </si>
-  <si>
-    <t>라철수</t>
-  </si>
-  <si>
-    <t>010-1111-5555</t>
-  </si>
-  <si>
-    <t>하</t>
-  </si>
-  <si>
-    <t>마철수</t>
-  </si>
-  <si>
-    <t>010-1111-6666</t>
+    <t>개인</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;₩&quot;* #,##0_-;\-&quot;₩&quot;* #,##0_-;_-&quot;₩&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;₩&quot;* #,##0.00_-;\-&quot;₩&quot;* #,##0.00_-;_-&quot;₩&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-1010412]h:mm"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -754,11 +675,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1294,13 +1212,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.4" outlineLevelRow="1" outlineLevelCol="5"/>
   <cols>
-    <col min="3" max="3" width="14.4" customWidth="1"/>
+    <col min="1" max="1" width="13.3" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="13.6" customWidth="1"/>
+    <col min="4" max="5" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1319,334 +1241,26 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="C2">
+        <v>900101</v>
+      </c>
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="E2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2">
-        <v>830319</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.541666666666667</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.8125</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3">
-        <v>910815</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.708333333333333</v>
-      </c>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4">
-        <v>940325</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.708333333333333</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0.645833333333333</v>
-      </c>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" t="s">
-        <v>23</v>
-      </c>
-      <c r="O4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5">
-        <v>740103</v>
-      </c>
-      <c r="C5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0.708333333333333</v>
-      </c>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6">
-        <v>670309</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.625</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0.708333333333333</v>
-      </c>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-    </row>
-    <row r="13" spans="1:15">
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
